--- a/public/backend_assets/file/sample_import.xlsx
+++ b/public/backend_assets/file/sample_import.xlsx
@@ -54,166 +54,166 @@
     <t>Shopee</t>
   </si>
   <si>
+    <t>Vehicle service</t>
+  </si>
+  <si>
+    <t>shopee.vn</t>
+  </si>
+  <si>
+    <t>Leading e-commerce platform in Southeast Asia</t>
+  </si>
+  <si>
+    <t>50% Off</t>
+  </si>
+  <si>
+    <t>SALE20</t>
+  </si>
+  <si>
+    <t>20% Off</t>
+  </si>
+  <si>
+    <t>https://shopee.vn</t>
+  </si>
+  <si>
+    <t>NEWUSER15</t>
+  </si>
+  <si>
+    <t>15% Off</t>
+  </si>
+  <si>
+    <t>FREESHIP</t>
+  </si>
+  <si>
+    <t>Free Shipping</t>
+  </si>
+  <si>
+    <t>SHOP10</t>
+  </si>
+  <si>
+    <t>$10 Off</t>
+  </si>
+  <si>
+    <t>Lazada</t>
+  </si>
+  <si>
+    <t>Underwear</t>
+  </si>
+  <si>
+    <t>lazada.vn</t>
+  </si>
+  <si>
+    <t>Leading online shopping platform</t>
+  </si>
+  <si>
+    <t>40% Off</t>
+  </si>
+  <si>
+    <t>LAZ40</t>
+  </si>
+  <si>
+    <t>https://lazada.vn</t>
+  </si>
+  <si>
+    <t>FLASH50</t>
+  </si>
+  <si>
+    <t>Danh sách danh mục (Copy tên danh mục vào cột "Danh mục" bên sheet chính)</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>Toys &amp; Hobbies</t>
+  </si>
+  <si>
+    <t>Sportswear</t>
+  </si>
+  <si>
+    <t>Software and services</t>
+  </si>
+  <si>
+    <t>Shoes and sandals</t>
+  </si>
+  <si>
+    <t>Retail</t>
+  </si>
+  <si>
+    <t>Phone accessories</t>
+  </si>
+  <si>
+    <t>Pets</t>
+  </si>
+  <si>
+    <t>Houseware</t>
+  </si>
+  <si>
+    <t>Home Garden</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>Hairdressing accessories</t>
+  </si>
+  <si>
+    <t>Gaming and esports</t>
+  </si>
+  <si>
+    <t>For businesses</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>Financial services and products</t>
+  </si>
+  <si>
+    <t>Fashion jewelry</t>
+  </si>
+  <si>
+    <t>Equipment furniture</t>
+  </si>
+  <si>
+    <t>Entertainment and media</t>
+  </si>
+  <si>
+    <t>Electronics and Technology</t>
+  </si>
+  <si>
+    <t>Education and Training</t>
+  </si>
+  <si>
+    <t>Drinks</t>
+  </si>
+  <si>
+    <t>Decorations</t>
+  </si>
+  <si>
+    <t>Computers and accessories</t>
+  </si>
+  <si>
+    <t>Clothing accessories</t>
+  </si>
+  <si>
+    <t>Books</t>
+  </si>
+  <si>
+    <t>Bedding</t>
+  </si>
+  <si>
+    <t>Beauty &amp; Health</t>
+  </si>
+  <si>
+    <t>Babies and kids</t>
+  </si>
+  <si>
+    <t>Automobiles &amp; Motorcycles</t>
+  </si>
+  <si>
+    <t>Art</t>
+  </si>
+  <si>
     <t>Adult products</t>
-  </si>
-  <si>
-    <t>shopee.vn</t>
-  </si>
-  <si>
-    <t>Leading e-commerce platform in Southeast Asia</t>
-  </si>
-  <si>
-    <t>50% Off</t>
-  </si>
-  <si>
-    <t>SALE20</t>
-  </si>
-  <si>
-    <t>20% Off</t>
-  </si>
-  <si>
-    <t>https://shopee.vn</t>
-  </si>
-  <si>
-    <t>NEWUSER15</t>
-  </si>
-  <si>
-    <t>15% Off</t>
-  </si>
-  <si>
-    <t>FREESHIP</t>
-  </si>
-  <si>
-    <t>Free Shipping</t>
-  </si>
-  <si>
-    <t>SHOP10</t>
-  </si>
-  <si>
-    <t>$10 Off</t>
-  </si>
-  <si>
-    <t>Lazada</t>
-  </si>
-  <si>
-    <t>Art</t>
-  </si>
-  <si>
-    <t>lazada.vn</t>
-  </si>
-  <si>
-    <t>Leading online shopping platform</t>
-  </si>
-  <si>
-    <t>40% Off</t>
-  </si>
-  <si>
-    <t>LAZ40</t>
-  </si>
-  <si>
-    <t>https://lazada.vn</t>
-  </si>
-  <si>
-    <t>FLASH50</t>
-  </si>
-  <si>
-    <t>Danh sách danh mục (Copy tên danh mục vào cột "Danh mục" bên sheet chính)</t>
-  </si>
-  <si>
-    <t>Automobiles &amp; Motorcycles</t>
-  </si>
-  <si>
-    <t>Babies and kids</t>
-  </si>
-  <si>
-    <t>Beauty &amp; Health</t>
-  </si>
-  <si>
-    <t>Bedding</t>
-  </si>
-  <si>
-    <t>Books</t>
-  </si>
-  <si>
-    <t>Clothing accessories</t>
-  </si>
-  <si>
-    <t>Computers and accessories</t>
-  </si>
-  <si>
-    <t>Decorations</t>
-  </si>
-  <si>
-    <t>Drinks</t>
-  </si>
-  <si>
-    <t>Education and Training</t>
-  </si>
-  <si>
-    <t>Electronics and Technology</t>
-  </si>
-  <si>
-    <t>Entertainment and media</t>
-  </si>
-  <si>
-    <t>Equipment furniture</t>
-  </si>
-  <si>
-    <t>Fashion jewelry</t>
-  </si>
-  <si>
-    <t>Financial services and products</t>
-  </si>
-  <si>
-    <t>Food</t>
-  </si>
-  <si>
-    <t>For businesses</t>
-  </si>
-  <si>
-    <t>Gaming and esports</t>
-  </si>
-  <si>
-    <t>Hairdressing accessories</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>Home Garden</t>
-  </si>
-  <si>
-    <t>Houseware</t>
-  </si>
-  <si>
-    <t>Pets</t>
-  </si>
-  <si>
-    <t>Phone accessories</t>
-  </si>
-  <si>
-    <t>Retail</t>
-  </si>
-  <si>
-    <t>Shoes and sandals</t>
-  </si>
-  <si>
-    <t>Software and services</t>
-  </si>
-  <si>
-    <t>Sportswear</t>
-  </si>
-  <si>
-    <t>Toys &amp; Hobbies</t>
-  </si>
-  <si>
-    <t>Travel</t>
-  </si>
-  <si>
-    <t>Underwear</t>
-  </si>
-  <si>
-    <t>Vehicle service</t>
   </si>
 </sst>
 </file>
@@ -587,7 +587,7 @@
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="18.71" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="11.711" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="54.13" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="18.71" bestFit="true" customWidth="true" style="0"/>
